--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297965</v>
       </c>
       <c r="B2" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129297968</v>
       </c>
       <c r="B3" t="n">
-        <v>91734</v>
+        <v>91741</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129297949</v>
+        <v>129297964</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>91899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610851</v>
+        <v>610998</v>
       </c>
       <c r="R4" t="n">
-        <v>7002392</v>
+        <v>7002588</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129297964</v>
+        <v>129297949</v>
       </c>
       <c r="B5" t="n">
-        <v>91892</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610998</v>
+        <v>610851</v>
       </c>
       <c r="R5" t="n">
-        <v>7002588</v>
+        <v>7002392</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>129297969</v>
       </c>
       <c r="B7" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129297948</v>
       </c>
       <c r="B9" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297970</v>
+        <v>129297966</v>
       </c>
       <c r="B10" t="n">
-        <v>100857</v>
+        <v>80104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610872</v>
+        <v>610994</v>
       </c>
       <c r="R10" t="n">
-        <v>7002614</v>
+        <v>7002623</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129297966</v>
+        <v>129297970</v>
       </c>
       <c r="B11" t="n">
-        <v>80104</v>
+        <v>100864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>610994</v>
+        <v>610872</v>
       </c>
       <c r="R11" t="n">
-        <v>7002623</v>
+        <v>7002614</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297965</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129297968</v>
       </c>
       <c r="B3" t="n">
-        <v>91741</v>
+        <v>91743</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129297964</v>
       </c>
       <c r="B4" t="n">
-        <v>91899</v>
+        <v>91901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129297949</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129297967</v>
       </c>
       <c r="B6" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129297969</v>
       </c>
       <c r="B7" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129297947</v>
       </c>
       <c r="B8" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129297948</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129297966</v>
       </c>
       <c r="B10" t="n">
-        <v>80104</v>
+        <v>80106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129297970</v>
       </c>
       <c r="B11" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129297964</v>
+        <v>129297949</v>
       </c>
       <c r="B4" t="n">
-        <v>91901</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610998</v>
+        <v>610851</v>
       </c>
       <c r="R4" t="n">
-        <v>7002588</v>
+        <v>7002392</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129297949</v>
+        <v>129297964</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>91901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610851</v>
+        <v>610998</v>
       </c>
       <c r="R5" t="n">
-        <v>7002392</v>
+        <v>7002588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297966</v>
+        <v>129297970</v>
       </c>
       <c r="B10" t="n">
-        <v>80106</v>
+        <v>100866</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610994</v>
+        <v>610872</v>
       </c>
       <c r="R10" t="n">
-        <v>7002623</v>
+        <v>7002614</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129297970</v>
+        <v>129297966</v>
       </c>
       <c r="B11" t="n">
-        <v>100866</v>
+        <v>80106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>610872</v>
+        <v>610994</v>
       </c>
       <c r="R11" t="n">
-        <v>7002614</v>
+        <v>7002623</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129297949</v>
+        <v>129297964</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>91901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610851</v>
+        <v>610998</v>
       </c>
       <c r="R4" t="n">
-        <v>7002392</v>
+        <v>7002588</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129297964</v>
+        <v>129297949</v>
       </c>
       <c r="B5" t="n">
-        <v>91901</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610998</v>
+        <v>610851</v>
       </c>
       <c r="R5" t="n">
-        <v>7002588</v>
+        <v>7002392</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297965</v>
       </c>
       <c r="B2" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129297968</v>
       </c>
       <c r="B3" t="n">
-        <v>91743</v>
+        <v>91752</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129297964</v>
+        <v>129297949</v>
       </c>
       <c r="B4" t="n">
-        <v>91901</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610998</v>
+        <v>610851</v>
       </c>
       <c r="R4" t="n">
-        <v>7002588</v>
+        <v>7002392</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129297949</v>
+        <v>129297964</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>91910</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610851</v>
+        <v>610998</v>
       </c>
       <c r="R5" t="n">
-        <v>7002392</v>
+        <v>7002588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>129297969</v>
       </c>
       <c r="B7" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129297948</v>
       </c>
       <c r="B9" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129297970</v>
       </c>
       <c r="B10" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129297968</v>
       </c>
       <c r="B3" t="n">
-        <v>91752</v>
+        <v>91753</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129297964</v>
       </c>
       <c r="B5" t="n">
-        <v>91910</v>
+        <v>91911</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129297969</v>
       </c>
       <c r="B7" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129297970</v>
       </c>
       <c r="B10" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -1454,7 +1454,7 @@
         <v>129297970</v>
       </c>
       <c r="B10" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297965</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129297968</v>
       </c>
       <c r="B3" t="n">
-        <v>91753</v>
+        <v>91756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129297949</v>
+        <v>129297964</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>91914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610851</v>
+        <v>610998</v>
       </c>
       <c r="R4" t="n">
-        <v>7002392</v>
+        <v>7002588</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129297964</v>
+        <v>129297949</v>
       </c>
       <c r="B5" t="n">
-        <v>91911</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610998</v>
+        <v>610851</v>
       </c>
       <c r="R5" t="n">
-        <v>7002588</v>
+        <v>7002392</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>129297967</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129297969</v>
       </c>
       <c r="B7" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129297947</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129297948</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297970</v>
+        <v>129297966</v>
       </c>
       <c r="B10" t="n">
-        <v>100895</v>
+        <v>80108</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610872</v>
+        <v>610994</v>
       </c>
       <c r="R10" t="n">
-        <v>7002614</v>
+        <v>7002623</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129297966</v>
+        <v>129297970</v>
       </c>
       <c r="B11" t="n">
-        <v>80106</v>
+        <v>100899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>610994</v>
+        <v>610872</v>
       </c>
       <c r="R11" t="n">
-        <v>7002623</v>
+        <v>7002614</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129297964</v>
+        <v>129297949</v>
       </c>
       <c r="B4" t="n">
-        <v>91914</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610998</v>
+        <v>610851</v>
       </c>
       <c r="R4" t="n">
-        <v>7002588</v>
+        <v>7002392</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129297949</v>
+        <v>129297964</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>91914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610851</v>
+        <v>610998</v>
       </c>
       <c r="R5" t="n">
-        <v>7002392</v>
+        <v>7002588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297965</v>
       </c>
       <c r="B2" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129297968</v>
       </c>
       <c r="B3" t="n">
-        <v>91756</v>
+        <v>91758</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129297949</v>
+        <v>129297964</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>91916</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610851</v>
+        <v>610998</v>
       </c>
       <c r="R4" t="n">
-        <v>7002392</v>
+        <v>7002588</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129297964</v>
+        <v>129297949</v>
       </c>
       <c r="B5" t="n">
-        <v>91914</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610998</v>
+        <v>610851</v>
       </c>
       <c r="R5" t="n">
-        <v>7002588</v>
+        <v>7002392</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>129297967</v>
       </c>
       <c r="B6" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129297969</v>
       </c>
       <c r="B7" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129297947</v>
       </c>
       <c r="B8" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129297948</v>
       </c>
       <c r="B9" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297966</v>
+        <v>129297970</v>
       </c>
       <c r="B10" t="n">
-        <v>80108</v>
+        <v>100901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610994</v>
+        <v>610872</v>
       </c>
       <c r="R10" t="n">
-        <v>7002623</v>
+        <v>7002614</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129297970</v>
+        <v>129297966</v>
       </c>
       <c r="B11" t="n">
-        <v>100899</v>
+        <v>80109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>610872</v>
+        <v>610994</v>
       </c>
       <c r="R11" t="n">
-        <v>7002614</v>
+        <v>7002623</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297965</v>
       </c>
       <c r="B2" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129297968</v>
       </c>
       <c r="B3" t="n">
-        <v>91758</v>
+        <v>91762</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129297964</v>
       </c>
       <c r="B4" t="n">
-        <v>91916</v>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129297969</v>
       </c>
       <c r="B7" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129297948</v>
       </c>
       <c r="B9" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129297970</v>
       </c>
       <c r="B10" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297965</v>
       </c>
       <c r="B2" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129297968</v>
       </c>
       <c r="B3" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129297964</v>
+        <v>129297949</v>
       </c>
       <c r="B4" t="n">
-        <v>91920</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610998</v>
+        <v>610851</v>
       </c>
       <c r="R4" t="n">
-        <v>7002588</v>
+        <v>7002392</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129297949</v>
+        <v>129297964</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>91921</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610851</v>
+        <v>610998</v>
       </c>
       <c r="R5" t="n">
-        <v>7002392</v>
+        <v>7002588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>129297969</v>
       </c>
       <c r="B7" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129297948</v>
       </c>
       <c r="B9" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297970</v>
+        <v>129297966</v>
       </c>
       <c r="B10" t="n">
-        <v>100905</v>
+        <v>80109</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610872</v>
+        <v>610994</v>
       </c>
       <c r="R10" t="n">
-        <v>7002614</v>
+        <v>7002623</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129297966</v>
+        <v>129297970</v>
       </c>
       <c r="B11" t="n">
-        <v>80109</v>
+        <v>100913</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>610994</v>
+        <v>610872</v>
       </c>
       <c r="R11" t="n">
-        <v>7002623</v>
+        <v>7002614</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129297949</v>
+        <v>129297964</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>91921</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610851</v>
+        <v>610998</v>
       </c>
       <c r="R4" t="n">
-        <v>7002392</v>
+        <v>7002588</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129297964</v>
+        <v>129297949</v>
       </c>
       <c r="B5" t="n">
-        <v>91921</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610998</v>
+        <v>610851</v>
       </c>
       <c r="R5" t="n">
-        <v>7002588</v>
+        <v>7002392</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297966</v>
+        <v>129297970</v>
       </c>
       <c r="B10" t="n">
-        <v>80109</v>
+        <v>100913</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610994</v>
+        <v>610872</v>
       </c>
       <c r="R10" t="n">
-        <v>7002623</v>
+        <v>7002614</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129297970</v>
+        <v>129297966</v>
       </c>
       <c r="B11" t="n">
-        <v>100913</v>
+        <v>80109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>610872</v>
+        <v>610994</v>
       </c>
       <c r="R11" t="n">
-        <v>7002614</v>
+        <v>7002623</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297965</v>
       </c>
       <c r="B2" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129297968</v>
       </c>
       <c r="B3" t="n">
-        <v>91763</v>
+        <v>91766</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129297964</v>
       </c>
       <c r="B4" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129297969</v>
       </c>
       <c r="B7" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129297948</v>
       </c>
       <c r="B9" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297970</v>
+        <v>129297966</v>
       </c>
       <c r="B10" t="n">
-        <v>100913</v>
+        <v>80109</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610872</v>
+        <v>610994</v>
       </c>
       <c r="R10" t="n">
-        <v>7002614</v>
+        <v>7002623</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129297966</v>
+        <v>129297970</v>
       </c>
       <c r="B11" t="n">
-        <v>80109</v>
+        <v>100916</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>610994</v>
+        <v>610872</v>
       </c>
       <c r="R11" t="n">
-        <v>7002623</v>
+        <v>7002614</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297966</v>
+        <v>129297970</v>
       </c>
       <c r="B10" t="n">
-        <v>80109</v>
+        <v>100916</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610994</v>
+        <v>610872</v>
       </c>
       <c r="R10" t="n">
-        <v>7002623</v>
+        <v>7002614</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129297970</v>
+        <v>129297966</v>
       </c>
       <c r="B11" t="n">
-        <v>100916</v>
+        <v>80109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>610872</v>
+        <v>610994</v>
       </c>
       <c r="R11" t="n">
-        <v>7002614</v>
+        <v>7002623</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129297964</v>
+        <v>129297949</v>
       </c>
       <c r="B4" t="n">
-        <v>91924</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610998</v>
+        <v>610851</v>
       </c>
       <c r="R4" t="n">
-        <v>7002588</v>
+        <v>7002392</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129297949</v>
+        <v>129297964</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>91924</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610851</v>
+        <v>610998</v>
       </c>
       <c r="R5" t="n">
-        <v>7002392</v>
+        <v>7002588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129297949</v>
+        <v>129297964</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>91924</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610851</v>
+        <v>610998</v>
       </c>
       <c r="R4" t="n">
-        <v>7002392</v>
+        <v>7002588</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129297964</v>
+        <v>129297949</v>
       </c>
       <c r="B5" t="n">
-        <v>91924</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610998</v>
+        <v>610851</v>
       </c>
       <c r="R5" t="n">
-        <v>7002588</v>
+        <v>7002392</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297965</v>
       </c>
       <c r="B2" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129297968</v>
       </c>
       <c r="B3" t="n">
-        <v>91766</v>
+        <v>91794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129297964</v>
       </c>
       <c r="B4" t="n">
-        <v>91924</v>
+        <v>91952</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129297949</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129297967</v>
       </c>
       <c r="B6" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129297969</v>
       </c>
       <c r="B7" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129297947</v>
       </c>
       <c r="B8" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129297948</v>
       </c>
       <c r="B9" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129297970</v>
       </c>
       <c r="B10" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129297966</v>
       </c>
       <c r="B11" t="n">
-        <v>80109</v>
+        <v>80135</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297965</v>
       </c>
       <c r="B2" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129297968</v>
       </c>
       <c r="B3" t="n">
-        <v>91794</v>
+        <v>91800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129297964</v>
       </c>
       <c r="B4" t="n">
-        <v>91952</v>
+        <v>91958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129297949</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129297967</v>
       </c>
       <c r="B6" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129297969</v>
       </c>
       <c r="B7" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129297947</v>
       </c>
       <c r="B8" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129297948</v>
       </c>
       <c r="B9" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129297970</v>
       </c>
       <c r="B10" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129297966</v>
       </c>
       <c r="B11" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297965</v>
       </c>
       <c r="B2" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129297968</v>
       </c>
       <c r="B3" t="n">
-        <v>91800</v>
+        <v>91801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129297964</v>
       </c>
       <c r="B4" t="n">
-        <v>91958</v>
+        <v>91959</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129297949</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129297967</v>
       </c>
       <c r="B6" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129297969</v>
       </c>
       <c r="B7" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129297947</v>
       </c>
       <c r="B8" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129297948</v>
       </c>
       <c r="B9" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129297970</v>
       </c>
       <c r="B10" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129297966</v>
       </c>
       <c r="B11" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129297965</v>
+        <v>129297968</v>
       </c>
       <c r="B2" t="n">
-        <v>91588</v>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>610998</v>
+        <v>610979</v>
       </c>
       <c r="R2" t="n">
-        <v>7002588</v>
+        <v>7002614</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129297968</v>
+        <v>129297969</v>
       </c>
       <c r="B3" t="n">
-        <v>91801</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>610979</v>
+        <v>610968</v>
       </c>
       <c r="R3" t="n">
-        <v>7002614</v>
+        <v>7002610</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129297964</v>
+        <v>129297948</v>
       </c>
       <c r="B4" t="n">
-        <v>91959</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610998</v>
+        <v>610870</v>
       </c>
       <c r="R4" t="n">
-        <v>7002588</v>
+        <v>7002365</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129297949</v>
+        <v>129297965</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610851</v>
+        <v>610998</v>
       </c>
       <c r="R5" t="n">
-        <v>7002392</v>
+        <v>7002588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129297967</v>
+        <v>129297956</v>
       </c>
       <c r="B6" t="n">
-        <v>80181</v>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>610994</v>
+        <v>610864</v>
       </c>
       <c r="R6" t="n">
-        <v>7002623</v>
+        <v>7002570</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129297969</v>
+        <v>129297964</v>
       </c>
       <c r="B7" t="n">
-        <v>91886</v>
+        <v>92281</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>610968</v>
+        <v>610998</v>
       </c>
       <c r="R7" t="n">
-        <v>7002610</v>
+        <v>7002588</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129297947</v>
+        <v>129297951</v>
       </c>
       <c r="B8" t="n">
-        <v>80181</v>
+        <v>92632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>610837</v>
+        <v>610903</v>
       </c>
       <c r="R8" t="n">
-        <v>7002356</v>
+        <v>7002489</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129297948</v>
+        <v>129297949</v>
       </c>
       <c r="B9" t="n">
-        <v>91588</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>610870</v>
+        <v>610851</v>
       </c>
       <c r="R9" t="n">
-        <v>7002365</v>
+        <v>7002392</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297970</v>
+        <v>129297950</v>
       </c>
       <c r="B10" t="n">
-        <v>100958</v>
+        <v>83290</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>6439</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610872</v>
+        <v>610886</v>
       </c>
       <c r="R10" t="n">
-        <v>7002614</v>
+        <v>7002478</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129297966</v>
+        <v>129297947</v>
       </c>
       <c r="B11" t="n">
-        <v>80141</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>610994</v>
+        <v>610837</v>
       </c>
       <c r="R11" t="n">
-        <v>7002623</v>
+        <v>7002356</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1642,6 +1642,588 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129297963</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lidberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>610942</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7002497</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129297967</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lidberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>610994</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7002623</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129297962</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lidberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>610916</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7002520</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129297970</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lidberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>610872</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7002614</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129297960</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lidberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>610916</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7002520</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129297966</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lidberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>610994</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7002623</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22215-2025 artfynd.xlsx
+++ b/artfynd/A 22215-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297968</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297969</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297948</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297965</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297956</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297964</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297951</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297949</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297950</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297947</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297963</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297967</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297962</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297970</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297960</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,8 +2304,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297966</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>